--- a/cashflow_ml/output/cashflow_workbook.xlsx
+++ b/cashflow_ml/output/cashflow_workbook.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="181">
   <si>
     <t xml:space="preserve">Cash In / Cash Out Summary</t>
   </si>
@@ -320,6 +320,48 @@
     <t xml:space="preserve">INV-HC-202603</t>
   </si>
   <si>
+    <t xml:space="preserve">RENT-COMM-04-202604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMTG-202604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-HC-202604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROOF REPAIR COMM-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORTHGATE BUILDING SERVICES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-NBS-8841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVICE CHARGE RECEIPT COMM-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-COMM-04-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DILAPIDATIONS SETTLEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORMER TENANT LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DILAP-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTALMENT TO HMRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT-2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total</t>
   </si>
   <si>
@@ -371,6 +413,12 @@
     <t xml:space="preserve">2026-03</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05</t>
+  </si>
+  <si>
     <t xml:space="preserve">Profit and loss</t>
   </si>
   <si>
@@ -383,6 +431,12 @@
     <t xml:space="preserve">    Rental income</t>
   </si>
   <si>
+    <t xml:space="preserve">    Service charge income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Uncategorised income</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total income</t>
   </si>
   <si>
@@ -395,18 +449,21 @@
     <t xml:space="preserve">    Managing agent fees</t>
   </si>
   <si>
+    <t xml:space="preserve">    Directors remuneration</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Insurance</t>
   </si>
   <si>
     <t xml:space="preserve">    Professional fees</t>
   </si>
   <si>
-    <t xml:space="preserve">    Directors remuneration</t>
-  </si>
-  <si>
     <t xml:space="preserve">    Repairs and maintenance</t>
   </si>
   <si>
+    <t xml:space="preserve">    Uncategorised expense</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total expenditure</t>
   </si>
   <si>
@@ -452,6 +509,12 @@
     <t xml:space="preserve">Income</t>
   </si>
   <si>
+    <t xml:space="preserve">SERVICE CHARGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service charge income</t>
+  </si>
+  <si>
     <t xml:space="preserve">MORTGAGE</t>
   </si>
   <si>
@@ -461,12 +524,18 @@
     <t xml:space="preserve">Expense</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEREST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANAGING AGENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managing agent fees</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGENT</t>
   </si>
   <si>
-    <t xml:space="preserve">Managing agent fees</t>
-  </si>
-  <si>
     <t xml:space="preserve">INSURANCE</t>
   </si>
   <si>
@@ -479,16 +548,31 @@
     <t xml:space="preserve">Professional fees</t>
   </si>
   <si>
-    <t xml:space="preserve">REMUNERATION</t>
+    <t xml:space="preserve">LEGAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRECTOR</t>
   </si>
   <si>
     <t xml:space="preserve">Directors remuneration</t>
   </si>
   <si>
+    <t xml:space="preserve">PAYROLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALARY</t>
+  </si>
+  <si>
     <t xml:space="preserve">REPAIR</t>
   </si>
   <si>
     <t xml:space="preserve">Repairs and maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAINTENANCE</t>
   </si>
   <si>
     <t xml:space="preserve">Blue text on yellow = input cells. Everything else in this workbook is calculated.</t>
@@ -914,8 +998,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblTransactions" displayName="tblTransactions" ref="A4:K43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:K43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblTransactions" displayName="tblTransactions" ref="A4:K50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:K50"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Description"/>
@@ -1147,8 +1231,8 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">SUM(Transactions!F5:F43)</f>
-        <v>38400</v>
+        <f aca="false">SUM(Transactions!F5:F50)</f>
+        <v>50050</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -1159,8 +1243,8 @@
         <v>7</v>
       </c>
       <c r="B6" s="7" t="n">
-        <f aca="false">SUM(Transactions!G5:G43)</f>
-        <v>32922</v>
+        <f aca="false">SUM(Transactions!G5:G50)</f>
+        <v>42836</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>8</v>
@@ -1171,8 +1255,8 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">SUM(Transactions!H5:H43)</f>
-        <v>5478</v>
+        <f aca="false">SUM(Transactions!H5:H50)</f>
+        <v>7214</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -1183,8 +1267,8 @@
         <v>11</v>
       </c>
       <c r="B8" s="9" t="n">
-        <f aca="false">SUM(Transactions!G5:G43)/SUM(Transactions!F5:F43)</f>
-        <v>0.85734375</v>
+        <f aca="false">SUM(Transactions!G5:G50)/SUM(Transactions!F5:F50)</f>
+        <v>0.855864135864136</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>12</v>
@@ -1195,8 +1279,8 @@
         <v>13</v>
       </c>
       <c r="B9" s="10" t="n">
-        <f aca="false">COUNT(Transactions!H5:H43)</f>
-        <v>39</v>
+        <f aca="false">COUNT(Transactions!H5:H50)</f>
+        <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>14</v>
@@ -1207,8 +1291,8 @@
         <v>15</v>
       </c>
       <c r="B10" s="11" t="n">
-        <f aca="false">COUNT('Monthly cash flow'!D5:D16)</f>
-        <v>12</v>
+        <f aca="false">COUNT('Monthly cash flow'!D5:D18)</f>
+        <v>14</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>16</v>
@@ -1219,7 +1303,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="10" t="n">
-        <f aca="false">COUNTBLANK(Transactions!E5:E43)</f>
+        <f aca="false">COUNTBLANK(Transactions!E5:E50)</f>
         <v>0</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1231,8 +1315,8 @@
         <v>19</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">MAX('Monthly cash flow'!D5:D16)</f>
-        <v>1494</v>
+        <f aca="false">MAX('Monthly cash flow'!D5:D18)</f>
+        <v>4100</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>20</v>
@@ -1243,7 +1327,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="5" t="n">
-        <f aca="false">MIN('Monthly cash flow'!D5:D16)</f>
+        <f aca="false">MIN('Monthly cash flow'!D5:D18)</f>
         <v>-7606</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1304,7 +1388,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1395,7 +1479,7 @@
         <v>Cash in</v>
       </c>
       <c r="J5" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B5))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B5))),0),0)),IF(H5&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K5" s="13" t="str">
@@ -1434,7 +1518,7 @@
         <v>Cash out</v>
       </c>
       <c r="J6" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B6))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B6))),0),0)),IF(H6&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K6" s="16" t="str">
@@ -1473,7 +1557,7 @@
         <v>Cash out</v>
       </c>
       <c r="J7" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B7))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B7))),0),0)),IF(H7&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K7" s="13" t="str">
@@ -1512,7 +1596,7 @@
         <v>Cash in</v>
       </c>
       <c r="J8" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B8))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B8))),0),0)),IF(H8&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K8" s="16" t="str">
@@ -1551,7 +1635,7 @@
         <v>Cash out</v>
       </c>
       <c r="J9" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B9))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B9))),0),0)),IF(H9&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K9" s="13" t="str">
@@ -1590,7 +1674,7 @@
         <v>Cash out</v>
       </c>
       <c r="J10" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B10))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B10))),0),0)),IF(H10&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K10" s="16" t="str">
@@ -1629,7 +1713,7 @@
         <v>Cash in</v>
       </c>
       <c r="J11" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B11))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B11))),0),0)),IF(H11&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K11" s="13" t="str">
@@ -1668,7 +1752,7 @@
         <v>Cash out</v>
       </c>
       <c r="J12" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B12))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B12))),0),0)),IF(H12&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K12" s="16" t="str">
@@ -1707,7 +1791,7 @@
         <v>Cash out</v>
       </c>
       <c r="J13" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B13))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B13))),0),0)),IF(H13&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K13" s="13" t="str">
@@ -1746,7 +1830,7 @@
         <v>Cash out</v>
       </c>
       <c r="J14" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B14))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B14))),0),0)),IF(H14&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Directors remuneration</v>
       </c>
       <c r="K14" s="16" t="str">
@@ -1785,7 +1869,7 @@
         <v>Cash in</v>
       </c>
       <c r="J15" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B15))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B15))),0),0)),IF(H15&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K15" s="13" t="str">
@@ -1824,7 +1908,7 @@
         <v>Cash out</v>
       </c>
       <c r="J16" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B16))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B16))),0),0)),IF(H16&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K16" s="16" t="str">
@@ -1863,7 +1947,7 @@
         <v>Cash out</v>
       </c>
       <c r="J17" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B17))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B17))),0),0)),IF(H17&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K17" s="13" t="str">
@@ -1902,7 +1986,7 @@
         <v>Cash out</v>
       </c>
       <c r="J18" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B18))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B18))),0),0)),IF(H18&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Insurance</v>
       </c>
       <c r="K18" s="16" t="str">
@@ -1941,7 +2025,7 @@
         <v>Cash in</v>
       </c>
       <c r="J19" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B19))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B19))),0),0)),IF(H19&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K19" s="13" t="str">
@@ -1980,7 +2064,7 @@
         <v>Cash out</v>
       </c>
       <c r="J20" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B20))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B20))),0),0)),IF(H20&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K20" s="16" t="str">
@@ -2019,7 +2103,7 @@
         <v>Cash out</v>
       </c>
       <c r="J21" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B21))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B21))),0),0)),IF(H21&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K21" s="13" t="str">
@@ -2058,7 +2142,7 @@
         <v>Cash in</v>
       </c>
       <c r="J22" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B22))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B22))),0),0)),IF(H22&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K22" s="16" t="str">
@@ -2097,7 +2181,7 @@
         <v>Cash out</v>
       </c>
       <c r="J23" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B23))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B23))),0),0)),IF(H23&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K23" s="13" t="str">
@@ -2136,7 +2220,7 @@
         <v>Cash out</v>
       </c>
       <c r="J24" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B24))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B24))),0),0)),IF(H24&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K24" s="16" t="str">
@@ -2175,7 +2259,7 @@
         <v>Cash in</v>
       </c>
       <c r="J25" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B25))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B25))),0),0)),IF(H25&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K25" s="13" t="str">
@@ -2214,7 +2298,7 @@
         <v>Cash out</v>
       </c>
       <c r="J26" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B26))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B26))),0),0)),IF(H26&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K26" s="16" t="str">
@@ -2253,7 +2337,7 @@
         <v>Cash out</v>
       </c>
       <c r="J27" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B27))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B27))),0),0)),IF(H27&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K27" s="13" t="str">
@@ -2292,7 +2376,7 @@
         <v>Cash in</v>
       </c>
       <c r="J28" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B28))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B28))),0),0)),IF(H28&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K28" s="16" t="str">
@@ -2331,7 +2415,7 @@
         <v>Cash out</v>
       </c>
       <c r="J29" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B29))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B29))),0),0)),IF(H29&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K29" s="13" t="str">
@@ -2370,7 +2454,7 @@
         <v>Cash out</v>
       </c>
       <c r="J30" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B30))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B30))),0),0)),IF(H30&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K30" s="16" t="str">
@@ -2409,7 +2493,7 @@
         <v>Cash in</v>
       </c>
       <c r="J31" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B31))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B31))),0),0)),IF(H31&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K31" s="13" t="str">
@@ -2448,7 +2532,7 @@
         <v>Cash out</v>
       </c>
       <c r="J32" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B32))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B32))),0),0)),IF(H32&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K32" s="16" t="str">
@@ -2487,7 +2571,7 @@
         <v>Cash out</v>
       </c>
       <c r="J33" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B33))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B33))),0),0)),IF(H33&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K33" s="13" t="str">
@@ -2526,7 +2610,7 @@
         <v>Cash in</v>
       </c>
       <c r="J34" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B34))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B34))),0),0)),IF(H34&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K34" s="16" t="str">
@@ -2565,7 +2649,7 @@
         <v>Cash out</v>
       </c>
       <c r="J35" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B35))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B35))),0),0)),IF(H35&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K35" s="13" t="str">
@@ -2604,7 +2688,7 @@
         <v>Cash out</v>
       </c>
       <c r="J36" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B36))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B36))),0),0)),IF(H36&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K36" s="16" t="str">
@@ -2643,7 +2727,7 @@
         <v>Cash in</v>
       </c>
       <c r="J37" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B37))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B37))),0),0)),IF(H37&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K37" s="13" t="str">
@@ -2682,7 +2766,7 @@
         <v>Cash out</v>
       </c>
       <c r="J38" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B38))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B38))),0),0)),IF(H38&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K38" s="16" t="str">
@@ -2721,7 +2805,7 @@
         <v>Cash out</v>
       </c>
       <c r="J39" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B39))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B39))),0),0)),IF(H39&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K39" s="13" t="str">
@@ -2760,7 +2844,7 @@
         <v>Cash out</v>
       </c>
       <c r="J40" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B40))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B40))),0),0)),IF(H40&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Professional fees</v>
       </c>
       <c r="K40" s="16" t="str">
@@ -2799,7 +2883,7 @@
         <v>Cash in</v>
       </c>
       <c r="J41" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B41))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B41))),0),0)),IF(H41&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Rental income</v>
       </c>
       <c r="K41" s="13" t="str">
@@ -2838,7 +2922,7 @@
         <v>Cash out</v>
       </c>
       <c r="J42" s="16" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B42))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B42))),0),0)),IF(H42&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Mortgage interest</v>
       </c>
       <c r="K42" s="16" t="str">
@@ -2877,7 +2961,7 @@
         <v>Cash out</v>
       </c>
       <c r="J43" s="13" t="str">
-        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$11,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$11,UPPER($B43))),0),0)),"Uncategorised")</f>
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B43))),0),0)),IF(H43&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
         <v>Managing agent fees</v>
       </c>
       <c r="K43" s="13" t="str">
@@ -2886,28 +2970,301 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="19" t="s">
+      <c r="A44" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F44" s="20" t="n">
-        <f aca="false">SUM(F5:F43)</f>
-        <v>38400</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <f aca="false">SUM(G5:G43)</f>
-        <v>32922</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <f aca="false">SUM(H5:H43)</f>
-        <v>5478</v>
-      </c>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
+      <c r="F44" s="17" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <f aca="false">F44-G44</f>
+        <v>3300</v>
+      </c>
+      <c r="I44" s="16" t="str">
+        <f aca="false">IF(H44&gt;=0,"Cash in","Cash out")</f>
+        <v>Cash in</v>
+      </c>
+      <c r="J44" s="16" t="str">
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B44))),0),0)),IF(H44&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
+        <v>Rental income</v>
+      </c>
+      <c r="K44" s="16" t="str">
+        <f aca="false">TEXT(A44,"yyyy-mm")</f>
+        <v>2026-04</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="12" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <f aca="false">F45-G45</f>
+        <v>-1450</v>
+      </c>
+      <c r="I45" s="13" t="str">
+        <f aca="false">IF(H45&gt;=0,"Cash in","Cash out")</f>
+        <v>Cash out</v>
+      </c>
+      <c r="J45" s="13" t="str">
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B45))),0),0)),IF(H45&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
+        <v>Mortgage interest</v>
+      </c>
+      <c r="K45" s="13" t="str">
+        <f aca="false">TEXT(A45,"yyyy-mm")</f>
+        <v>2026-04</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>264</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <f aca="false">F46-G46</f>
+        <v>-264</v>
+      </c>
+      <c r="I46" s="16" t="str">
+        <f aca="false">IF(H46&gt;=0,"Cash in","Cash out")</f>
+        <v>Cash out</v>
+      </c>
+      <c r="J46" s="16" t="str">
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B46))),0),0)),IF(H46&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
+        <v>Managing agent fees</v>
+      </c>
+      <c r="K46" s="16" t="str">
+        <f aca="false">TEXT(A46,"yyyy-mm")</f>
+        <v>2026-04</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="12" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <f aca="false">F47-G47</f>
+        <v>-4800</v>
+      </c>
+      <c r="I47" s="13" t="str">
+        <f aca="false">IF(H47&gt;=0,"Cash in","Cash out")</f>
+        <v>Cash out</v>
+      </c>
+      <c r="J47" s="13" t="str">
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B47))),0),0)),IF(H47&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
+        <v>Repairs and maintenance</v>
+      </c>
+      <c r="K47" s="13" t="str">
+        <f aca="false">TEXT(A47,"yyyy-mm")</f>
+        <v>2026-04</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>850</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <f aca="false">F48-G48</f>
+        <v>850</v>
+      </c>
+      <c r="I48" s="16" t="str">
+        <f aca="false">IF(H48&gt;=0,"Cash in","Cash out")</f>
+        <v>Cash in</v>
+      </c>
+      <c r="J48" s="16" t="str">
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B48))),0),0)),IF(H48&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
+        <v>Service charge income</v>
+      </c>
+      <c r="K48" s="16" t="str">
+        <f aca="false">TEXT(A48,"yyyy-mm")</f>
+        <v>2026-04</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="12" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <f aca="false">F49-G49</f>
+        <v>7500</v>
+      </c>
+      <c r="I49" s="13" t="str">
+        <f aca="false">IF(H49&gt;=0,"Cash in","Cash out")</f>
+        <v>Cash in</v>
+      </c>
+      <c r="J49" s="13" t="str">
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B49))),0),0)),IF(H49&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
+        <v>Uncategorised income</v>
+      </c>
+      <c r="K49" s="13" t="str">
+        <f aca="false">TEXT(A49,"yyyy-mm")</f>
+        <v>2026-05</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>3400</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <f aca="false">F50-G50</f>
+        <v>-3400</v>
+      </c>
+      <c r="I50" s="16" t="str">
+        <f aca="false">IF(H50&gt;=0,"Cash in","Cash out")</f>
+        <v>Cash out</v>
+      </c>
+      <c r="J50" s="16" t="str">
+        <f aca="false">IFERROR(INDEX(Categories!$B$5:$B$19,MATCH(1,INDEX(--ISNUMBER(SEARCH(Categories!$A$5:$A$19,UPPER($B50))),0),0)),IF(H50&gt;=0,"Uncategorised income","Uncategorised expense"))</f>
+        <v>Uncategorised expense</v>
+      </c>
+      <c r="K50" s="16" t="str">
+        <f aca="false">TEXT(A50,"yyyy-mm")</f>
+        <v>2026-05</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F51" s="20" t="n">
+        <f aca="false">SUM(F5:F50)</f>
+        <v>50050</v>
+      </c>
+      <c r="G51" s="20" t="n">
+        <f aca="false">SUM(G5:G50)</f>
+        <v>42836</v>
+      </c>
+      <c r="H51" s="20" t="n">
+        <f aca="false">SUM(H5:H50)</f>
+        <v>7214</v>
+      </c>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2928,7 +3285,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -2938,12 +3295,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2958,22 +3315,22 @@
         <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B5" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A5)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A5)</f>
         <v>3200</v>
       </c>
       <c r="C5" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A5)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A5)</f>
         <v>1706</v>
       </c>
       <c r="D5" s="14" t="n">
@@ -2987,14 +3344,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B6" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A6)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A6)</f>
         <v>3200</v>
       </c>
       <c r="C6" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A6)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A6)</f>
         <v>1706</v>
       </c>
       <c r="D6" s="17" t="n">
@@ -3008,14 +3365,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B7" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A7)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A7)</f>
         <v>3200</v>
       </c>
       <c r="C7" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A7)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A7)</f>
         <v>10806</v>
       </c>
       <c r="D7" s="14" t="n">
@@ -3029,14 +3386,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B8" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A8)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A8)</f>
         <v>3200</v>
       </c>
       <c r="C8" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A8)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A8)</f>
         <v>2956</v>
       </c>
       <c r="D8" s="17" t="n">
@@ -3050,14 +3407,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B9" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A9)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A9)</f>
         <v>3200</v>
       </c>
       <c r="C9" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A9)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A9)</f>
         <v>1706</v>
       </c>
       <c r="D9" s="14" t="n">
@@ -3071,14 +3428,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B10" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A10)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A10)</f>
         <v>3200</v>
       </c>
       <c r="C10" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A10)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A10)</f>
         <v>1706</v>
       </c>
       <c r="D10" s="17" t="n">
@@ -3092,14 +3449,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B11" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A11)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A11)</f>
         <v>3200</v>
       </c>
       <c r="C11" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A11)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A11)</f>
         <v>1706</v>
       </c>
       <c r="D11" s="14" t="n">
@@ -3113,14 +3470,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B12" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A12)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A12)</f>
         <v>3200</v>
       </c>
       <c r="C12" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A12)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A12)</f>
         <v>1706</v>
       </c>
       <c r="D12" s="17" t="n">
@@ -3134,14 +3491,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="B13" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A13)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A13)</f>
         <v>3200</v>
       </c>
       <c r="C13" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A13)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A13)</f>
         <v>1706</v>
       </c>
       <c r="D13" s="14" t="n">
@@ -3155,14 +3512,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B14" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A14)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A14)</f>
         <v>3200</v>
       </c>
       <c r="C14" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A14)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A14)</f>
         <v>1706</v>
       </c>
       <c r="D14" s="17" t="n">
@@ -3176,14 +3533,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B15" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A15)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A15)</f>
         <v>3200</v>
       </c>
       <c r="C15" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A15)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A15)</f>
         <v>3806</v>
       </c>
       <c r="D15" s="14" t="n">
@@ -3197,14 +3554,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B16" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$K$5:$K$43,$A16)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A16)</f>
         <v>3200</v>
       </c>
       <c r="C16" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$K$5:$K$43,$A16)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A16)</f>
         <v>1706</v>
       </c>
       <c r="D16" s="17" t="n">
@@ -3217,22 +3574,64 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="20" t="n">
-        <f aca="false">SUM(B5:B16)</f>
-        <v>38400</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <f aca="false">SUM(C5:C16)</f>
-        <v>32922</v>
-      </c>
-      <c r="D17" s="20" t="n">
-        <f aca="false">SUM(D5:D16)</f>
-        <v>5478</v>
-      </c>
-      <c r="E17" s="18"/>
+      <c r="A17" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A17)</f>
+        <v>4150</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A17)</f>
+        <v>6514</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <f aca="false">B17-C17</f>
+        <v>-2364</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <f aca="false">E16+D17</f>
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$K$5:$K$50,$A18)</f>
+        <v>7500</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$K$5:$K$50,$A18)</f>
+        <v>3400</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <f aca="false">B18-C18</f>
+        <v>4100</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <f aca="false">E17+D18</f>
+        <v>7214</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="20" t="n">
+        <f aca="false">SUM(B5:B18)</f>
+        <v>50050</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <f aca="false">SUM(C5:C18)</f>
+        <v>42836</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <f aca="false">SUM(D5:D18)</f>
+        <v>7214</v>
+      </c>
+      <c r="E19" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3250,7 +3649,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -3260,12 +3659,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3280,157 +3679,196 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="B6" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$J$5:$J$43,"Rental income")</f>
-        <v>12</v>
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Rental income")</f>
+        <v>13</v>
       </c>
       <c r="C6" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$J$5:$J$43,"Rental income")</f>
-        <v>38400</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Rental income")</f>
+        <v>41700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22" t="n">
-        <f aca="false">SUM(C6:C6)</f>
-        <v>38400</v>
+      <c r="A7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Service charge income")</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Service charge income")</f>
+        <v>850</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
+      <c r="A8" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Uncategorised income")</f>
+        <v>1</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Uncategorised income")</f>
+        <v>7500</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
+      <c r="A9" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22" t="n">
+        <f aca="false">SUM(C6:C8)</f>
+        <v>50050</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$J$5:$J$43,"Mortgage interest")</f>
-        <v>12</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$J$5:$J$43,"Mortgage interest")</f>
-        <v>-17400</v>
-      </c>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$J$5:$J$43,"Managing agent fees")</f>
-        <v>12</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$J$5:$J$43,"Managing agent fees")</f>
-        <v>-3072</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B12" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$J$5:$J$43,"Insurance")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Mortgage interest")</f>
+        <v>13</v>
       </c>
       <c r="C12" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$J$5:$J$43,"Insurance")</f>
-        <v>-1250</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Mortgage interest")</f>
+        <v>-18850</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B13" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$J$5:$J$43,"Professional fees")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Managing agent fees")</f>
+        <v>13</v>
       </c>
       <c r="C13" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$J$5:$J$43,"Professional fees")</f>
-        <v>-2100</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Managing agent fees")</f>
+        <v>-3336</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B14" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$J$5:$J$43,"Directors remuneration")</f>
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Directors remuneration")</f>
         <v>1</v>
       </c>
       <c r="C14" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$J$5:$J$43,"Directors remuneration")</f>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Directors remuneration")</f>
         <v>-9100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B15" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$J$5:$J$43,"Repairs and maintenance")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Insurance")</f>
+        <v>1</v>
       </c>
       <c r="C15" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$J$5:$J$43,"Repairs and maintenance")</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Insurance")</f>
+        <v>-1250</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="22" t="n">
-        <f aca="false">SUM(C10:C15)</f>
-        <v>-32922</v>
+      <c r="A16" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="13" t="n">
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Professional fees")</f>
+        <v>1</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Professional fees")</f>
+        <v>-2100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Repairs and maintenance")</f>
+        <v>1</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Repairs and maintenance")</f>
+        <v>-4800</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="24" t="n">
-        <f aca="false">C7+C16</f>
-        <v>5478</v>
+      <c r="A18" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <f aca="false">COUNTIFS(Transactions!$J$5:$J$50,"Uncategorised expense")</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$J$5:$J$50,"Uncategorised expense")</f>
+        <v>-3400</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22" t="n">
+        <f aca="false">SUM(C12:C18)</f>
+        <v>-42836</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
-        <v>126</v>
+      <c r="A21" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="23"/>
+      <c r="C21" s="24" t="n">
+        <f aca="false">C9+C19</f>
+        <v>7214</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3449,7 +3887,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -3460,18 +3898,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
@@ -3483,10 +3921,10 @@
         <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3494,24 +3932,24 @@
         <v>43</v>
       </c>
       <c r="B5" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$C$5:$C$43,$A5)</f>
-        <v>12</v>
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A5)</f>
+        <v>14</v>
       </c>
       <c r="C5" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$C$5:$C$43,$A5)</f>
-        <v>38400</v>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A5)</f>
+        <v>42550</v>
       </c>
       <c r="D5" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$C$5:$C$43,$A5)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A5)</f>
         <v>0</v>
       </c>
       <c r="E5" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$C$5:$C$43,$A5)</f>
-        <v>38400</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A5)</f>
+        <v>42550</v>
       </c>
       <c r="F5" s="26" t="n">
-        <f aca="false">IF(E5&gt;=0,C5/SUM(Transactions!$F$5:$F$43),D5/SUM(Transactions!$G$5:$G$43))</f>
-        <v>1</v>
+        <f aca="false">IF(E5&gt;=0,C5/SUM(Transactions!$F$5:$F$50),D5/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.85014985014985</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3519,24 +3957,24 @@
         <v>47</v>
       </c>
       <c r="B6" s="16" t="n">
-        <f aca="false">COUNTIFS(Transactions!$C$5:$C$43,$A6)</f>
-        <v>12</v>
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A6)</f>
+        <v>13</v>
       </c>
       <c r="C6" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$C$5:$C$43,$A6)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A6)</f>
         <v>0</v>
       </c>
       <c r="D6" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$C$5:$C$43,$A6)</f>
-        <v>17400</v>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A6)</f>
+        <v>18850</v>
       </c>
       <c r="E6" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$C$5:$C$43,$A6)</f>
-        <v>-17400</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A6)</f>
+        <v>-18850</v>
       </c>
       <c r="F6" s="27" t="n">
-        <f aca="false">IF(E6&gt;=0,C6/SUM(Transactions!$F$5:$F$43),D6/SUM(Transactions!$G$5:$G$43))</f>
-        <v>0.528521960998724</v>
+        <f aca="false">IF(E6&gt;=0,C6/SUM(Transactions!$F$5:$F$50),D6/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.440050424876272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3544,122 +3982,197 @@
         <v>59</v>
       </c>
       <c r="B7" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$C$5:$C$43,$A7)</f>
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$C$5:$C$43,$A7)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A7)</f>
         <v>0</v>
       </c>
       <c r="D7" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$C$5:$C$43,$A7)</f>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A7)</f>
         <v>9100</v>
       </c>
       <c r="E7" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$C$5:$C$43,$A7)</f>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A7)</f>
         <v>-9100</v>
       </c>
       <c r="F7" s="26" t="n">
-        <f aca="false">IF(E7&gt;=0,C7/SUM(Transactions!$F$5:$F$43),D7/SUM(Transactions!$G$5:$G$43))</f>
-        <v>0.276410910637264</v>
+        <f aca="false">IF(E7&gt;=0,C7/SUM(Transactions!$F$5:$F$50),D7/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.212438136147166</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIFS(Transactions!$C$5:$C$43,$A8)</f>
-        <v>12</v>
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A8)</f>
+        <v>1</v>
       </c>
       <c r="C8" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$C$5:$C$43,$A8)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A8)</f>
+        <v>7500</v>
       </c>
       <c r="D8" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$C$5:$C$43,$A8)</f>
-        <v>3072</v>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A8)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$C$5:$C$43,$A8)</f>
-        <v>-3072</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A8)</f>
+        <v>7500</v>
       </c>
       <c r="F8" s="27" t="n">
-        <f aca="false">IF(E8&gt;=0,C8/SUM(Transactions!$F$5:$F$43),D8/SUM(Transactions!$G$5:$G$43))</f>
-        <v>0.0933114634590851</v>
+        <f aca="false">IF(E8&gt;=0,C8/SUM(Transactions!$F$5:$F$50),D8/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.14985014985015</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B9" s="13" t="n">
-        <f aca="false">COUNTIFS(Transactions!$C$5:$C$43,$A9)</f>
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A9)</f>
         <v>1</v>
       </c>
       <c r="C9" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$C$5:$C$43,$A9)</f>
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A9)</f>
         <v>0</v>
       </c>
       <c r="D9" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$C$5:$C$43,$A9)</f>
-        <v>2100</v>
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A9)</f>
+        <v>4800</v>
       </c>
       <c r="E9" s="14" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$C$5:$C$43,$A9)</f>
-        <v>-2100</v>
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A9)</f>
+        <v>-4800</v>
       </c>
       <c r="F9" s="26" t="n">
-        <f aca="false">IF(E9&gt;=0,C9/SUM(Transactions!$F$5:$F$43),D9/SUM(Transactions!$G$5:$G$43))</f>
-        <v>0.063787133223984</v>
+        <f aca="false">IF(E9&gt;=0,C9/SUM(Transactions!$F$5:$F$50),D9/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.112055280605099</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A10)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A10)</f>
+        <v>3400</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A10)</f>
+        <v>-3400</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <f aca="false">IF(E10&gt;=0,C10/SUM(Transactions!$F$5:$F$50),D10/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.0793724904286114</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A11)</f>
+        <v>13</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A11)</f>
+        <v>3336</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A11)</f>
+        <v>-3336</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <f aca="false">IF(E11&gt;=0,C11/SUM(Transactions!$F$5:$F$50),D11/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.0778784200205435</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A12)</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A12)</f>
+        <v>2100</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A12)</f>
+        <v>-2100</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <f aca="false">IF(E12&gt;=0,C12/SUM(Transactions!$F$5:$F$50),D12/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.0490241852647306</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIFS(Transactions!$C$5:$C$43,$A10)</f>
+      <c r="B13" s="13" t="n">
+        <f aca="false">COUNTIFS(Transactions!$C$5:$C$50,$A13)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$5:$F$43,Transactions!$C$5:$C$43,$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$G$5:$G$43,Transactions!$C$5:$C$43,$A10)</f>
+      <c r="C13" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$5:$F$50,Transactions!$C$5:$C$50,$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$G$5:$G$50,Transactions!$C$5:$C$50,$A13)</f>
         <v>1250</v>
       </c>
-      <c r="E10" s="17" t="n">
-        <f aca="false">SUMIFS(Transactions!$H$5:$H$43,Transactions!$C$5:$C$43,$A10)</f>
+      <c r="E13" s="14" t="n">
+        <f aca="false">SUMIFS(Transactions!$H$5:$H$50,Transactions!$C$5:$C$50,$A13)</f>
         <v>-1250</v>
       </c>
-      <c r="F10" s="27" t="n">
-        <f aca="false">IF(E10&gt;=0,C10/SUM(Transactions!$F$5:$F$43),D10/SUM(Transactions!$G$5:$G$43))</f>
-        <v>0.0379685316809428</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="19" t="n">
-        <f aca="false">SUM(B5:B10)</f>
-        <v>39</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <f aca="false">SUM(C5:C10)</f>
-        <v>38400</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <f aca="false">SUM(D5:D10)</f>
-        <v>32922</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <f aca="false">SUM(E5:E10)</f>
-        <v>5478</v>
-      </c>
-      <c r="F11" s="18"/>
+      <c r="F13" s="26" t="n">
+        <f aca="false">IF(E13&gt;=0,C13/SUM(Transactions!$F$5:$F$50),D13/SUM(Transactions!$G$5:$G$50))</f>
+        <v>0.0291810626575777</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <f aca="false">SUM(B5:B13)</f>
+        <v>46</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <f aca="false">SUM(C5:C13)</f>
+        <v>50050</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <f aca="false">SUM(D5:D13)</f>
+        <v>42836</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <f aca="false">SUM(E5:E13)</f>
+        <v>7214</v>
+      </c>
+      <c r="F14" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3677,7 +4190,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -3687,106 +4200,194 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>141</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
-        <v>152</v>
+      <c r="A13" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
